--- a/pds_admin_WB/Backend/Backend/Result_Sheet_leg2.xlsx
+++ b/pds_admin_WB/Backend/Backend/Result_Sheet_leg2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>Scenario</t>
   </si>
@@ -79,13 +79,25 @@
     <t>WestBengal</t>
   </si>
   <si>
-    <t>Paschim Bardhaman</t>
+    <t>Darjeeling</t>
+  </si>
+  <si>
+    <t>Howrah</t>
   </si>
   <si>
     <t>Def</t>
   </si>
   <si>
     <t>Wholesale</t>
+  </si>
+  <si>
+    <t>AJOY NATH YADAV</t>
+  </si>
+  <si>
+    <t>Alipurduar</t>
+  </si>
+  <si>
+    <t>RR</t>
   </si>
   <si>
     <t>PR</t>
@@ -446,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -519,46 +531,102 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>1182</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>23.50248767</v>
+        <v>26.57895873</v>
       </c>
       <c r="H2">
-        <v>87.73095685</v>
+        <v>88.97369044</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N2">
-        <v>23.50248767</v>
+        <v>22.573481</v>
       </c>
       <c r="O2">
-        <v>87.73095685</v>
+        <v>88.23092200000001</v>
       </c>
       <c r="P2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2">
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>635.801</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3">
+        <v>81</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>22.559808</v>
+      </c>
+      <c r="H3">
+        <v>88.30919969999999</v>
+      </c>
+      <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="Q2">
-        <v>1222.15875</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3">
+        <v>22.573481</v>
+      </c>
+      <c r="O3">
+        <v>88.23092200000001</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3">
+        <v>96</v>
+      </c>
+      <c r="R3">
+        <v>10.6225</v>
       </c>
     </row>
   </sheetData>
